--- a/artfynd/A 39999-2025 artfynd.xlsx
+++ b/artfynd/A 39999-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>113679384</v>
       </c>
       <c r="B2" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80415</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,12 +770,12 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Helene Andersson, Tomas Rask</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -789,12 +784,7 @@
         <v>113679386</v>
       </c>
       <c r="B3" t="n">
-        <v>79518</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80375</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,12 +876,12 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Helene Andersson, Tomas Rask</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -900,12 +890,7 @@
         <v>113679387</v>
       </c>
       <c r="B4" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80415</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,12 +982,12 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Helene Andersson, Tomas Rask</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>
@@ -1011,12 +996,7 @@
         <v>113679385</v>
       </c>
       <c r="B5" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80415</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,12 +1088,12 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Helene Andersson, Tomas Rask</t>
+          <t>Tomas Rask</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naturvärdesinventering </t>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
     </row>

--- a/artfynd/A 39999-2025 artfynd.xlsx
+++ b/artfynd/A 39999-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113679384</v>
       </c>
       <c r="B2" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>113679386</v>
       </c>
       <c r="B3" t="n">
-        <v>80380</v>
+        <v>80382</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>113679387</v>
       </c>
       <c r="B4" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>113679385</v>
       </c>
       <c r="B5" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39999-2025 artfynd.xlsx
+++ b/artfynd/A 39999-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113679384</v>
       </c>
       <c r="B2" t="n">
-        <v>80422</v>
+        <v>80424</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>113679386</v>
       </c>
       <c r="B3" t="n">
-        <v>80382</v>
+        <v>80384</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>113679387</v>
       </c>
       <c r="B4" t="n">
-        <v>80422</v>
+        <v>80424</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>113679385</v>
       </c>
       <c r="B5" t="n">
-        <v>80422</v>
+        <v>80424</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 39999-2025 artfynd.xlsx
+++ b/artfynd/A 39999-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113679384</v>
       </c>
       <c r="B2" t="n">
-        <v>80424</v>
+        <v>80432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>113679386</v>
       </c>
       <c r="B3" t="n">
-        <v>80384</v>
+        <v>80392</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>113679387</v>
       </c>
       <c r="B4" t="n">
-        <v>80424</v>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>113679385</v>
       </c>
       <c r="B5" t="n">
-        <v>80424</v>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
